--- a/Digital-Business-Toolkit/07-CRM/Product.xlsx
+++ b/Digital-Business-Toolkit/07-CRM/Product.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Main Workspace" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Quick Start" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="User Guide" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="לוח בקרה" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="שולחן עבודה" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="התחלה מהירה" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="מדריך שימוש" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -652,7 +652,7 @@
     <row r="2" ht="46" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Contractor CRM — Dashboard</t>
+          <t>לוח בקרה — ניהול לקוחות ולידים</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
@@ -663,7 +663,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>ContractorOS — Never lose a lead again</t>
+          <t>ContractorOS — אף ליד לא ייעלם יותר</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -700,42 +700,42 @@
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="B6" s="6">
-        <f>COUNTA('Main Workspace'!A4:A38)</f>
+        <f>COUNTA('שולחן עבודה'!A4:A38)</f>
         <v/>
       </c>
       <c r="C6" s="7">
-        <f>IFERROR(COUNTIF('Main Workspace'!H4:H38,"נסגר בהצלחה")/COUNTA('Main Workspace'!A4:A38),0)</f>
+        <f>IFERROR(COUNTIF('שולחן עבודה'!H4:H38,"נסגר בהצלחה")/COUNTA('שולחן עבודה'!A4:A38),0)</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>SUM('Main Workspace'!G4:G38)</f>
+        <f>SUM('שולחן עבודה'!G4:G38)</f>
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>SUMIF('Main Workspace'!H4:H38,"נסגר בהצלחה",'Main Workspace'!G4:G38)</f>
+        <f>SUMIF('שולחן עבודה'!H4:H38,"נסגר בהצלחה",'שולחן עבודה'!G4:G38)</f>
         <v/>
       </c>
       <c r="F6" s="6">
-        <f>COUNTIFS('Main Workspace'!I4:I38,"חם",'Main Workspace'!H4:H38,"&lt;&gt;נסגר בהצלחה",'Main Workspace'!H4:H38,"&lt;&gt;אבדנו")</f>
+        <f>COUNTIFS('שולחן עבודה'!I4:I38,"חם",'שולחן עבודה'!H4:H38,"&lt;&gt;נסגר בהצלחה",'שולחן עבודה'!H4:H38,"&lt;&gt;אבדנו")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>⚠ Business Insights / התראות</t>
+          <t>⚠ תובנות עסקיות והתראות</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="B10" s="9">
-        <f>IF(COUNTIFS('Main Workspace'!J4:J38,"&lt;="&amp;TODAY(),'Main Workspace'!J4:J38,"&gt;0")&gt;0,"יש "&amp;COUNTIFS('Main Workspace'!J4:J38,"&lt;="&amp;TODAY(),'Main Workspace'!J4:J38,"&gt;0")&amp;" לידים שדורשים פולואפ היום או שכבר עבר.","אין פולואפים דחופים כרגע.")</f>
+        <f>IF(COUNTIFS('שולחן עבודה'!J4:J38,"&lt;="&amp;TODAY(),'שולחן עבודה'!J4:J38,"&gt;0")&gt;0,"יש "&amp;COUNTIFS('שולחן עבודה'!J4:J38,"&lt;="&amp;TODAY(),'שולחן עבודה'!J4:J38,"&gt;0")&amp;" לידים שדורשים פולואפ היום או שכבר עבר.","אין פולואפים דחופים כרגע.")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="B11" s="10">
-        <f>IF(COUNTIFS('Main Workspace'!I4:I38,"חם",'Main Workspace'!H4:H38,"&lt;&gt;נסגר בהצלחה")&gt;0,"יש לידים חמים שעדיין לא נסגרו — תעדפו אותם.","אין לידים חמים פתוחים כרגע.")</f>
+        <f>IF(COUNTIFS('שולחן עבודה'!I4:I38,"חם",'שולחן עבודה'!H4:H38,"&lt;&gt;נסגר בהצלחה")&gt;0,"יש לידים חמים שעדיין לא נסגרו — תעדפו אותם.","אין לידים חמים פתוחים כרגע.")</f>
         <v/>
       </c>
     </row>
@@ -777,7 +777,7 @@
     <row r="1" ht="44" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>ניהול לקוחות ולידים | Contractor CRM</t>
+          <t>ניהול לקוחות ולידים</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -794,7 +794,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>הזינו נתונים בתאים הצהובים בלבד — Dashboard מתעדכן אוטומטית</t>
+          <t>הזינו נתונים בתאים הצהובים בלבד — לוח הבקרה מתעדכן אוטומטית</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -821,7 +821,7 @@
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>דוא"ל</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -1563,7 +1563,7 @@
     <row r="1" ht="44" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>התחלה מהירה | Quick Start</t>
+          <t>התחלה מהירה</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1579,7 +1579,7 @@
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="22" t="inlineStr">
         <is>
-          <t>1. עברו ללשונית 'Main Workspace'.</t>
+          <t>1. עברו ללשונית 'שולחן עבודה'.</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="22" t="inlineStr">
         <is>
-          <t>5. עברו ל-Dashboard לראות אחוז המרה, פוטנציאל כולל, והכנסה שנסגרה.</t>
+          <t>5. עברו ל-לוח הבקרה לראות אחוז המרה, פוטנציאל כולל, והכנסה שנסגרה.</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
     <row r="1" ht="44" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>מדריך שימוש | User Guide</t>
+          <t>מדריך שימוש</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="C8" s="25" t="inlineStr">
         <is>
-          <t>שם, טלפון, Email, מקור ליד, סוג עבודה, אזור, סכום פוטנציאלי, סטטוס, חום ליד, תאריך פולואפ.</t>
+          <t>שם, טלפון, דוא"ל, מקור ליד, סוג עבודה, אזור, סכום פוטנציאלי, סטטוס, חום ליד, תאריך פולואפ.</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
     <row r="10" ht="46" customHeight="1">
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>מה Dashboard מציג?</t>
+          <t>מה לוח הבקרה מציג?</t>
         </is>
       </c>
       <c r="C10" s="25" t="inlineStr">
@@ -1765,7 +1765,7 @@
     <row r="13">
       <c r="B13" s="26" t="inlineStr">
         <is>
-          <t>שאלות נפוצות (FAQ)</t>
+          <t>שאלות נפוצות</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C14" s="25" t="inlineStr">
         <is>
-          <t>ה-Dashboard סופר אוטומטית לידים עם תאריך פולואפ שהגיע או עבר.</t>
+          <t>לוח הבקרה סופר אוטומטית לידים עם תאריך פולואפ שהגיע או עבר.</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="C16" s="25" t="inlineStr">
         <is>
-          <t>עדכנו סטטוס ל'נסגר בהצלחה' — הסכום נספר אוטומטית כהכנסה שנסגרה ב-Dashboard.</t>
+          <t>עדכנו סטטוס ל'נסגר בהצלחה' — הסכום נספר אוטומטית כהכנסה שנסגרה בלוח הבקרה.</t>
         </is>
       </c>
     </row>

--- a/Digital-Business-Toolkit/07-CRM/Product.xlsx
+++ b/Digital-Business-Toolkit/07-CRM/Product.xlsx
@@ -663,7 +663,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>ContractorOS — אף ליד לא ייעלם יותר</t>
+          <t>JobMargin — אף ליד לא ייעלם יותר</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
